--- a/tests/fixtures/excel_cumplimiento.xlsx
+++ b/tests/fixtures/excel_cumplimiento.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,81 +426,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>RIT</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>RUT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>NOMBRE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>TRIBUNAL</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>DERIVACION</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>FEC. NACIMIENTO</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>EDAD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CURADOR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FEC. OIDO</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DIAS DE CUMPLIMIENTO</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>FEC.INGRESO EFECTIVO</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>FEC.EGRESO PROYECTADO</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FEC.ACT.F.RESIDENCIAL</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FEC.ACT.F.INDIVIDUAL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FEC.ACT.F.FAE</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>DIAS PARA EGRESAR</t>
         </is>
@@ -528,20 +545,23 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
+      <c r="J2" t="n">
+        <v>10</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>400</v>
       </c>
     </row>
@@ -573,7 +593,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09/07/2008</t>
+          <t>14/07/2008</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,28 +607,31 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
+      <c r="J3" t="n">
+        <v>100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -650,20 +673,23 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>22/12/2025</t>
-        </is>
+      <c r="J4" t="n">
+        <v>200</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>55</v>
       </c>
     </row>
@@ -695,7 +721,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23/08/2009</t>
+          <t>28/08/2009</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -709,20 +735,23 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
+      <c r="J5" t="n">
+        <v>15</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>200</v>
       </c>
     </row>
@@ -764,28 +793,31 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>13/09/2025</t>
-        </is>
+      <c r="J6" t="n">
+        <v>300</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -827,28 +859,31 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
+      <c r="J7" t="n">
+        <v>50</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>30</v>
       </c>
     </row>
@@ -890,28 +925,31 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>25/02/2025</t>
-        </is>
+      <c r="J8" t="n">
+        <v>500</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>300</v>
       </c>
     </row>
@@ -953,28 +991,31 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
+      <c r="J9" t="n">
+        <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>400</v>
       </c>
     </row>
@@ -1012,28 +1053,31 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
+      <c r="J10" t="n">
+        <v>90</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25/02/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1075,20 +1119,23 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10/02/2026</t>
-        </is>
+      <c r="J11" t="n">
+        <v>150</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17/11/2024</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>22/11/2024</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>600</v>
       </c>
     </row>
@@ -1130,20 +1177,23 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
+      <c r="J12" t="n">
+        <v>25</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09/08/2024</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>14/08/2024</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1185,20 +1235,23 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>05/06/2025</t>
-        </is>
+      <c r="J13" t="n">
+        <v>400</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01/05/2024</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>06/05/2024</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>800</v>
       </c>
     </row>
@@ -1240,20 +1293,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
+      <c r="J14" t="n">
+        <v>10</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>27/01/2024</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>900</v>
       </c>
     </row>
@@ -1295,20 +1351,23 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>22/12/2025</t>
-        </is>
+      <c r="J15" t="n">
+        <v>200</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14/10/2023</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>19/10/2023</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1350,28 +1409,31 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
+      <c r="J16" t="n">
+        <v>35</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06/07/2023</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28/03/2023</t>
+          <t>11/07/2023</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>28/03/2023</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+          <t>02/04/2023</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02/04/2023</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -1413,28 +1475,31 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>05/06/2025</t>
-        </is>
+      <c r="J17" t="n">
+        <v>400</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28/03/2023</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>02/04/2023</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -1472,28 +1537,31 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>25/02/2025</t>
-        </is>
+      <c r="J18" t="n">
+        <v>500</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18/12/2022</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/12/2022</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>1300</v>
       </c>
     </row>
@@ -1535,28 +1603,31 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>17/11/2024</t>
-        </is>
+      <c r="J19" t="n">
+        <v>600</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09/09/2022</t>
+          <t>22/11/2024</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>14/09/2022</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>1400</v>
       </c>
     </row>
@@ -1598,20 +1669,23 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>09/08/2024</t>
-        </is>
+      <c r="J20" t="n">
+        <v>700</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>01/06/2022</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>14/08/2024</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>06/06/2022</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -1653,28 +1727,31 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>01/05/2024</t>
-        </is>
+      <c r="J21" t="n">
+        <v>800</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21/02/2022</t>
+          <t>06/05/2024</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
+          <t>26/02/2022</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22/11/2025</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -1716,24 +1793,27 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>07/03/2026</t>
-        </is>
+      <c r="J22" t="n">
+        <v>125</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13/11/2021</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>18/11/2021</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>07/03/2026</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
         <v>1700</v>
       </c>
     </row>
@@ -1775,20 +1855,23 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>02/03/2026</t>
-        </is>
+      <c r="J23" t="n">
+        <v>130</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>05/08/2021</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>10/08/2021</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -1830,20 +1913,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>22/01/2024</t>
-        </is>
+      <c r="J24" t="n">
+        <v>900</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>27/04/2021</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>27/01/2024</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>02/05/2021</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>1900</v>
       </c>
     </row>
@@ -1885,20 +1971,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>14/10/2023</t>
-        </is>
+      <c r="J25" t="n">
+        <v>1000</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17/01/2021</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>19/10/2023</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>22/01/2021</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -1941,23 +2030,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>06/07/2023</t>
-        </is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1100</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09/10/2020</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>11/07/2023</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>14/10/2020</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>2100</v>
       </c>
     </row>
@@ -1976,32 +2068,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>RIT</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>RUT MENOR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>NOMBRE MENOR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>TRIBUNAL</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>NOMBRE CENTRO</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>FECHA VENCIMIENTO</t>
         </is>
@@ -2035,7 +2127,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2159,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2191,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2223,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2255,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
     </row>
